--- a/Mendez_Ex3A_tables.xlsx
+++ b/Mendez_Ex3A_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denaemendez\Documents\DATA_Labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F8FECB5-D8EF-483B-9D31-E332BD142078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E28BF5E8-835D-43C1-9154-A9C0454857DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>Customer_ID</t>
   </si>
@@ -80,7 +80,25 @@
     <t>Time</t>
   </si>
   <si>
-    <t>Duration</t>
+    <t>Imani</t>
+  </si>
+  <si>
+    <t>Imani1999@yahoo.com</t>
+  </si>
+  <si>
+    <t>302-555-5555</t>
+  </si>
+  <si>
+    <t>8 west 8th street</t>
+  </si>
+  <si>
+    <t>Hummy</t>
+  </si>
+  <si>
+    <t>Poodle</t>
+  </si>
+  <si>
+    <t>Duration (in minutes)</t>
   </si>
 </sst>
 </file>
@@ -96,7 +114,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -115,6 +133,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -128,10 +152,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,12 +474,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.109375" customWidth="1"/>
     <col min="5" max="5" width="27.44140625" customWidth="1"/>
   </cols>
@@ -473,6 +501,23 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1234</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -480,7 +525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6CF68E0-DE82-4D41-AFBC-8528E275F6CF}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -507,6 +552,23 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1234</v>
+      </c>
+      <c r="B2">
+        <v>1111</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -514,27 +576,47 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81435033-1175-4883-A6FB-19B5C9E064B0}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="1" max="2" width="23.44140625" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" customWidth="1"/>
+    <col min="5" max="5" width="18.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" t="s">
-        <v>12</v>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2234</v>
+      </c>
+      <c r="B2">
+        <v>1234</v>
+      </c>
+      <c r="C2" s="4">
+        <v>46326</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +626,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B9669B-A833-434C-837B-83D7E1C883CD}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -558,6 +640,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>2234</v>
+      </c>
+      <c r="B2">
+        <v>1111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
